--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0008500000000000001</v>
+        <v>-0.00038</v>
       </c>
       <c r="E2">
-        <v>-0.006310000000000001</v>
+        <v>0.0233</v>
       </c>
       <c r="G2">
-        <v>0.131782698741437</v>
+        <v>0.1015226792718495</v>
       </c>
       <c r="H2">
-        <v>0.131782698741437</v>
+        <v>0.1015226792718495</v>
       </c>
       <c r="I2">
-        <v>0.1265871435399076</v>
+        <v>0.06275973046364276</v>
       </c>
       <c r="J2">
-        <v>0.1113227626518724</v>
+        <v>0.0543945960915324</v>
       </c>
       <c r="K2">
-        <v>47.874</v>
+        <v>35.709</v>
       </c>
       <c r="L2">
-        <v>0.09533614784132548</v>
+        <v>0.0718274162727547</v>
       </c>
       <c r="M2">
-        <v>15.292</v>
+        <v>18.045</v>
       </c>
       <c r="N2">
-        <v>0.02589362818971502</v>
+        <v>0.04335655934646805</v>
       </c>
       <c r="O2">
-        <v>0.3194218155992814</v>
+        <v>0.5053347895488534</v>
       </c>
       <c r="P2">
-        <v>15.292</v>
+        <v>17.927</v>
       </c>
       <c r="Q2">
-        <v>0.02589362818971502</v>
+        <v>0.04307304180682364</v>
       </c>
       <c r="R2">
-        <v>0.3194218155992814</v>
+        <v>0.5020303004844717</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.00653920753671377</v>
       </c>
       <c r="U2">
-        <v>60.478</v>
+        <v>55.844</v>
       </c>
       <c r="V2">
-        <v>0.102406149990687</v>
+        <v>0.1341758769822201</v>
       </c>
       <c r="W2">
-        <v>0.07895640074211502</v>
+        <v>0.04617424242424242</v>
       </c>
       <c r="X2">
-        <v>0.06351415029650345</v>
+        <v>0.1027661890534286</v>
       </c>
       <c r="Y2">
-        <v>0.01544225044561157</v>
+        <v>-0.05659194662918621</v>
       </c>
       <c r="Z2">
-        <v>0.7138744635208387</v>
+        <v>0.6772597917611751</v>
       </c>
       <c r="AA2">
-        <v>0.07459905630580049</v>
+        <v>0.03448599823649693</v>
       </c>
       <c r="AB2">
-        <v>0.06322103227558379</v>
+        <v>0.1026263935157848</v>
       </c>
       <c r="AC2">
-        <v>0.01146284286360021</v>
+        <v>-0.06862680572859045</v>
       </c>
       <c r="AD2">
-        <v>14.253</v>
+        <v>13.659</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14.253</v>
+        <v>13.659</v>
       </c>
       <c r="AG2">
-        <v>-46.225</v>
+        <v>-42.185</v>
       </c>
       <c r="AH2">
-        <v>0.02356557207645874</v>
+        <v>0.03177553569891523</v>
       </c>
       <c r="AI2">
-        <v>0.01562909492046191</v>
+        <v>0.01721016204692443</v>
       </c>
       <c r="AJ2">
-        <v>-0.08491857186159514</v>
+        <v>-0.1127895940002406</v>
       </c>
       <c r="AK2">
-        <v>-0.0542881470389618</v>
+        <v>-0.05717557924411946</v>
       </c>
       <c r="AL2">
-        <v>1.558</v>
+        <v>1.199</v>
       </c>
       <c r="AM2">
-        <v>1.558</v>
+        <v>1.199</v>
       </c>
       <c r="AN2">
-        <v>0.1896783466191129</v>
+        <v>0.3059263572836409</v>
       </c>
       <c r="AO2">
-        <v>40.80038510911425</v>
+        <v>26.02251876563803</v>
       </c>
       <c r="AP2">
-        <v>-0.6151604274516589</v>
+        <v>-0.9448351549901451</v>
       </c>
       <c r="AQ2">
-        <v>40.80038510911425</v>
+        <v>26.02251876563803</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Asuransi Bina Dana Arta Tbk (IDX:ABDA)</t>
+          <t>PT Lippo General Insurance Tbk (IDX:LPGI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0832</v>
+        <v>0.132</v>
       </c>
       <c r="E3">
-        <v>0.05230000000000001</v>
+        <v>-0.0107</v>
       </c>
       <c r="G3">
-        <v>0.2618629173989455</v>
+        <v>0.0781733746130031</v>
       </c>
       <c r="H3">
-        <v>0.2618629173989455</v>
+        <v>0.0781733746130031</v>
       </c>
       <c r="I3">
-        <v>0.3163444639718805</v>
+        <v>0.07082043343653252</v>
       </c>
       <c r="J3">
-        <v>0.2329274416269144</v>
+        <v>0.0548031017621018</v>
       </c>
       <c r="K3">
-        <v>12.4</v>
+        <v>8.27</v>
       </c>
       <c r="L3">
-        <v>0.2179261862917399</v>
+        <v>0.0640092879256966</v>
       </c>
       <c r="M3">
-        <v>2.91</v>
+        <v>6.56</v>
       </c>
       <c r="N3">
-        <v>0.01144767899291896</v>
+        <v>0.05841495992876224</v>
       </c>
       <c r="O3">
-        <v>0.2346774193548387</v>
+        <v>0.7932285368802902</v>
       </c>
       <c r="P3">
-        <v>2.91</v>
+        <v>6.56</v>
       </c>
       <c r="Q3">
-        <v>0.01144767899291896</v>
+        <v>0.05841495992876224</v>
       </c>
       <c r="R3">
-        <v>0.2346774193548387</v>
+        <v>0.7932285368802902</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>24</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>0.0944138473642801</v>
+        <v>0.0201246660730187</v>
       </c>
       <c r="W3">
-        <v>0.1423650975889782</v>
+        <v>0.1174715909090909</v>
       </c>
       <c r="X3">
-        <v>0.06324748137860885</v>
+        <v>0.1025577817878172</v>
       </c>
       <c r="Y3">
-        <v>0.07911761621036935</v>
+        <v>0.01491380912127371</v>
       </c>
       <c r="Z3">
-        <v>1.258849557522124</v>
+        <v>1.874528466136614</v>
       </c>
       <c r="AA3">
-        <v>0.2932206068268016</v>
+        <v>0.1027299742856414</v>
       </c>
       <c r="AB3">
-        <v>0.06324748137860885</v>
+        <v>0.102545236751818</v>
       </c>
       <c r="AC3">
-        <v>0.2299731254481927</v>
+        <v>0.0001847375338234758</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AG3">
-        <v>-24</v>
+        <v>-2.217</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0003827563800147761</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.0007854885556144163</v>
       </c>
       <c r="AJ3">
-        <v>-0.104257167680278</v>
+        <v>-0.02013934939999818</v>
       </c>
       <c r="AK3">
-        <v>-0.310077519379845</v>
+        <v>-0.04224224987138692</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.004401228249744114</v>
+      </c>
+      <c r="AO3">
+        <v>508.3333333333334</v>
       </c>
       <c r="AP3">
-        <v>-1.290322580645161</v>
+        <v>-0.2269191402251791</v>
+      </c>
+      <c r="AQ3">
+        <v>508.3333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Lippo General Insurance Tbk (IDX:LPGI)</t>
+          <t>PT Asuransi Ramayana Tbk (IDX:ASRM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.117</v>
+        <v>0.197</v>
       </c>
       <c r="E4">
-        <v>0.359</v>
+        <v>0.0233</v>
       </c>
       <c r="G4">
-        <v>0.07196180555555555</v>
+        <v>0.03684633950120676</v>
       </c>
       <c r="H4">
-        <v>0.07196180555555555</v>
+        <v>0.03684633950120676</v>
       </c>
       <c r="I4">
-        <v>0.09375</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="J4">
-        <v>0.07790376106194691</v>
+        <v>0.02295078888054095</v>
       </c>
       <c r="K4">
-        <v>9.359999999999999</v>
+        <v>4.07</v>
       </c>
       <c r="L4">
-        <v>0.08124999999999999</v>
+        <v>0.03274336283185841</v>
       </c>
       <c r="M4">
-        <v>2.93</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>0.05689320388349515</v>
+        <v>0.03249211356466877</v>
       </c>
       <c r="O4">
-        <v>0.3130341880341881</v>
+        <v>0.2530712530712531</v>
       </c>
       <c r="P4">
-        <v>2.93</v>
+        <v>1.03</v>
       </c>
       <c r="Q4">
-        <v>0.05689320388349515</v>
+        <v>0.03249211356466877</v>
       </c>
       <c r="R4">
-        <v>0.3130341880341881</v>
+        <v>0.2530712530712531</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>6.55</v>
       </c>
       <c r="V4">
-        <v>0.03184466019417476</v>
+        <v>0.2066246056782334</v>
       </c>
       <c r="W4">
-        <v>0.1772727272727273</v>
+        <v>0.1068241469816273</v>
       </c>
       <c r="X4">
-        <v>0.06334714199054982</v>
+        <v>0.1038615413471803</v>
       </c>
       <c r="Y4">
-        <v>0.1139255852821775</v>
+        <v>0.002962605634447044</v>
       </c>
       <c r="Z4">
-        <v>2.253080383336593</v>
+        <v>3.623906705539359</v>
       </c>
       <c r="AA4">
-        <v>0.1755234358368137</v>
+        <v>0.08317151772161049</v>
       </c>
       <c r="AB4">
-        <v>0.06322764537535652</v>
+        <v>0.102814980614421</v>
       </c>
       <c r="AC4">
-        <v>0.1122957904614572</v>
+        <v>-0.01964346289281046</v>
       </c>
       <c r="AD4">
-        <v>0.164</v>
+        <v>0.775</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.164</v>
+        <v>0.775</v>
       </c>
       <c r="AG4">
-        <v>-1.476</v>
+        <v>-5.774999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.003174357386187674</v>
+        <v>0.02386451116243264</v>
       </c>
       <c r="AI4">
-        <v>0.002324131285074542</v>
+        <v>0.01983365323096609</v>
       </c>
       <c r="AJ4">
-        <v>-0.02950583719814489</v>
+        <v>-0.2227579556412729</v>
       </c>
       <c r="AK4">
-        <v>-0.02141489176484243</v>
+        <v>-0.1775557263643351</v>
       </c>
       <c r="AL4">
-        <v>0.027</v>
+        <v>0.139</v>
       </c>
       <c r="AM4">
-        <v>0.027</v>
+        <v>0.139</v>
       </c>
       <c r="AN4">
-        <v>0.0143859649122807</v>
+        <v>0.1942355889724311</v>
       </c>
       <c r="AO4">
-        <v>400.0000000000001</v>
+        <v>24.38848920863309</v>
       </c>
       <c r="AP4">
-        <v>-0.1294736842105263</v>
+        <v>-1.447368421052631</v>
       </c>
       <c r="AQ4">
-        <v>400.0000000000001</v>
+        <v>24.38848920863309</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Asuransi Ramayana Tbk (IDX:ASRM)</t>
+          <t>PT Asuransi Dayin Mitra Tbk (IDX:ASDM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.147</v>
+        <v>-0.0162</v>
       </c>
       <c r="E5">
-        <v>0.008579999999999999</v>
+        <v>-0.156</v>
       </c>
       <c r="G5">
-        <v>0.04417744916820703</v>
+        <v>0.1745614035087719</v>
       </c>
       <c r="H5">
-        <v>0.04417744916820703</v>
+        <v>0.1745614035087719</v>
       </c>
       <c r="I5">
-        <v>0.04362292051756007</v>
+        <v>0.09035087719298246</v>
       </c>
       <c r="J5">
-        <v>0.03688997912251588</v>
+        <v>0.08673684210526315</v>
       </c>
       <c r="K5">
-        <v>4.96</v>
+        <v>1.24</v>
       </c>
       <c r="L5">
-        <v>0.04584103512014787</v>
+        <v>0.1087719298245614</v>
       </c>
       <c r="M5">
-        <v>0.973</v>
+        <v>0.908</v>
       </c>
       <c r="N5">
-        <v>0.02695290858725762</v>
+        <v>0.08180180180180181</v>
       </c>
       <c r="O5">
-        <v>0.1961693548387097</v>
+        <v>0.7322580645161291</v>
       </c>
       <c r="P5">
-        <v>0.973</v>
+        <v>0.908</v>
       </c>
       <c r="Q5">
-        <v>0.02695290858725762</v>
+        <v>0.08180180180180181</v>
       </c>
       <c r="R5">
-        <v>0.1961693548387097</v>
+        <v>0.7322580645161291</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.98</v>
+        <v>0.889</v>
       </c>
       <c r="V5">
-        <v>0.1379501385041551</v>
+        <v>0.08009009009009009</v>
       </c>
       <c r="W5">
-        <v>0.1545171339563863</v>
+        <v>0.05166666666666667</v>
       </c>
       <c r="X5">
-        <v>0.06427044864224855</v>
+        <v>0.1030983253285956</v>
       </c>
       <c r="Y5">
-        <v>0.09024668531413772</v>
+        <v>-0.05143165866192893</v>
       </c>
       <c r="Z5">
-        <v>3.776614310645724</v>
+        <v>0.4870337933096937</v>
       </c>
       <c r="AA5">
-        <v>0.1393192230735154</v>
+        <v>0.04224377323023027</v>
       </c>
       <c r="AB5">
-        <v>0.0630496913223122</v>
+        <v>0.1027566983746112</v>
       </c>
       <c r="AC5">
-        <v>0.07626953175120324</v>
+        <v>-0.06051292514438091</v>
       </c>
       <c r="AD5">
-        <v>1.18</v>
+        <v>0.115</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.18</v>
+        <v>0.115</v>
       </c>
       <c r="AG5">
-        <v>-3.800000000000001</v>
+        <v>-0.774</v>
       </c>
       <c r="AH5">
-        <v>0.03165236051502145</v>
+        <v>0.01025412394115024</v>
       </c>
       <c r="AI5">
-        <v>0.03004073319755601</v>
+        <v>0.004932446922582029</v>
       </c>
       <c r="AJ5">
-        <v>-0.1176470588235294</v>
+        <v>-0.07495642068564788</v>
       </c>
       <c r="AK5">
-        <v>-0.1107871720116618</v>
+        <v>-0.03451351110318381</v>
       </c>
       <c r="AL5">
-        <v>0.141</v>
+        <v>0.025</v>
       </c>
       <c r="AM5">
-        <v>0.141</v>
+        <v>0.025</v>
       </c>
       <c r="AN5">
-        <v>0.2388663967611336</v>
+        <v>0.09583333333333334</v>
       </c>
       <c r="AO5">
-        <v>33.47517730496454</v>
+        <v>41.2</v>
       </c>
       <c r="AP5">
-        <v>-0.7692307692307693</v>
+        <v>-0.645</v>
       </c>
       <c r="AQ5">
-        <v>33.47517730496454</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Asuransi Dayin Mitra Tbk (IDX:ASDM)</t>
+          <t>PT Victoria Insurance Tbk (IDX:VINS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,46 +1124,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0008500000000000001</v>
+        <v>-0.0153</v>
       </c>
       <c r="E6">
-        <v>-0.0302</v>
+        <v>0.158</v>
       </c>
       <c r="G6">
-        <v>0.2095238095238095</v>
+        <v>0.3163636363636363</v>
       </c>
       <c r="H6">
-        <v>0.2095238095238095</v>
+        <v>0.3163636363636363</v>
       </c>
       <c r="I6">
-        <v>0.2031746031746032</v>
+        <v>0.1749090909090909</v>
       </c>
       <c r="J6">
-        <v>0.1716956195926153</v>
+        <v>0.1749090909090909</v>
       </c>
       <c r="K6">
-        <v>1.97</v>
+        <v>0.537</v>
       </c>
       <c r="L6">
-        <v>0.1563492063492063</v>
+        <v>0.1952727272727273</v>
       </c>
       <c r="M6">
-        <v>1.28</v>
+        <v>0.326</v>
       </c>
       <c r="N6">
-        <v>0.09999999999999999</v>
+        <v>0.01963855421686747</v>
       </c>
       <c r="O6">
-        <v>0.6497461928934011</v>
+        <v>0.6070763500931099</v>
       </c>
       <c r="P6">
-        <v>1.28</v>
+        <v>0.326</v>
       </c>
       <c r="Q6">
-        <v>0.09999999999999999</v>
+        <v>0.01963855421686747</v>
       </c>
       <c r="R6">
-        <v>0.6497461928934011</v>
+        <v>0.6070763500931099</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1166,73 +1172,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.9360000000000001</v>
+        <v>0.429</v>
       </c>
       <c r="V6">
-        <v>0.073125</v>
+        <v>0.0258433734939759</v>
       </c>
       <c r="W6">
-        <v>0.08954545454545454</v>
+        <v>0.04068181818181819</v>
       </c>
       <c r="X6">
-        <v>0.06408611270465267</v>
+        <v>0.1027100105583776</v>
       </c>
       <c r="Y6">
-        <v>0.02545934184080187</v>
+        <v>-0.06202819237655945</v>
       </c>
       <c r="Z6">
-        <v>0.6046065259117083</v>
+        <v>0.2194557497406432</v>
       </c>
       <c r="AA6">
-        <v>0.1038082920761494</v>
+        <v>0.03838480568190887</v>
       </c>
       <c r="AB6">
-        <v>0.06321441917581105</v>
+        <v>0.1026052144126047</v>
       </c>
       <c r="AC6">
-        <v>0.04059387290033832</v>
+        <v>-0.0642204087306958</v>
       </c>
       <c r="AD6">
-        <v>0.343</v>
+        <v>0.053</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.343</v>
+        <v>0.053</v>
       </c>
       <c r="AG6">
-        <v>-0.593</v>
+        <v>-0.376</v>
       </c>
       <c r="AH6">
-        <v>0.0260975424180172</v>
+        <v>0.003182609739986789</v>
       </c>
       <c r="AI6">
-        <v>0.01409029289734215</v>
+        <v>0.004548185016733888</v>
       </c>
       <c r="AJ6">
-        <v>-0.04857868436143196</v>
+        <v>-0.02317554240631164</v>
       </c>
       <c r="AK6">
-        <v>-0.02533430170461828</v>
+        <v>-0.03349964362081254</v>
       </c>
       <c r="AL6">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.116271186440678</v>
-      </c>
-      <c r="AO6">
-        <v>24.38095238095238</v>
+        <v>0.1041257367387033</v>
       </c>
       <c r="AP6">
-        <v>-0.2010169491525423</v>
-      </c>
-      <c r="AQ6">
-        <v>24.38095238095238</v>
+        <v>-0.7387033398821218</v>
       </c>
     </row>
     <row r="7">
@@ -1252,40 +1252,40 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.1956403269754768</v>
+        <v>0.1803450078410873</v>
       </c>
       <c r="H7">
-        <v>0.1956403269754768</v>
+        <v>0.1803450078410873</v>
       </c>
       <c r="I7">
-        <v>0.1580381471389646</v>
+        <v>0.1014113957135389</v>
       </c>
       <c r="J7">
-        <v>0.127388324663529</v>
+        <v>0.08704478132078758</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>21.7</v>
       </c>
       <c r="L7">
-        <v>0.09809264305177112</v>
+        <v>0.1134343962362781</v>
       </c>
       <c r="M7">
-        <v>6.6</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N7">
-        <v>0.03324937027707808</v>
+        <v>0.04539007092198582</v>
       </c>
       <c r="O7">
-        <v>0.3666666666666666</v>
+        <v>0.4129032258064517</v>
       </c>
       <c r="P7">
-        <v>6.6</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="Q7">
-        <v>0.03324937027707808</v>
+        <v>0.04539007092198582</v>
       </c>
       <c r="R7">
-        <v>0.3666666666666666</v>
+        <v>0.4129032258064517</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1294,73 +1294,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>26.4</v>
+        <v>42.7</v>
       </c>
       <c r="V7">
-        <v>0.1329974811083123</v>
+        <v>0.2163120567375887</v>
       </c>
       <c r="W7">
-        <v>0.03474903474903475</v>
+        <v>0.03885407341092211</v>
       </c>
       <c r="X7">
-        <v>0.06518672124572208</v>
+        <v>0.1059676657361218</v>
       </c>
       <c r="Y7">
-        <v>-0.03043768649668734</v>
+        <v>-0.06711359232519964</v>
       </c>
       <c r="Z7">
-        <v>0.3563106796116505</v>
+        <v>0.3513960323291698</v>
       </c>
       <c r="AA7">
-        <v>0.0453898205354516</v>
+        <v>0.03058719079108499</v>
       </c>
       <c r="AB7">
-        <v>0.06305800770858951</v>
+        <v>0.1036203935175701</v>
       </c>
       <c r="AC7">
-        <v>-0.0176681871731379</v>
+        <v>-0.07303320272648509</v>
       </c>
       <c r="AD7">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
-        <v>-14.1</v>
+        <v>-30.2</v>
       </c>
       <c r="AH7">
-        <v>0.05834914611005693</v>
+        <v>0.05955216769890424</v>
       </c>
       <c r="AI7">
-        <v>0.01984511132623427</v>
+        <v>0.02058290795323563</v>
       </c>
       <c r="AJ7">
-        <v>-0.0764642082429501</v>
+        <v>-0.180622009569378</v>
       </c>
       <c r="AK7">
-        <v>-0.02376137512639029</v>
+        <v>-0.05348919589089622</v>
       </c>
       <c r="AL7">
-        <v>1.23</v>
+        <v>0.925</v>
       </c>
       <c r="AM7">
-        <v>1.23</v>
+        <v>0.925</v>
       </c>
       <c r="AN7">
-        <v>0.3219895287958115</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="AO7">
-        <v>23.57723577235772</v>
+        <v>20.97297297297297</v>
       </c>
       <c r="AP7">
-        <v>-0.369109947643979</v>
+        <v>-0.9741935483870968</v>
       </c>
       <c r="AQ7">
-        <v>23.57723577235772</v>
+        <v>20.97297297297297</v>
       </c>
     </row>
     <row r="8">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Victoria Insurance Tbk (IDX:VINS)</t>
+          <t>PT Asuransi Jasa Tania Tbk (IDX:ASJT)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1380,115 +1380,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0103</v>
-      </c>
-      <c r="E8">
-        <v>-0.202</v>
+        <v>-0.108</v>
       </c>
       <c r="G8">
-        <v>0.1909090909090909</v>
+        <v>0.02895522388059701</v>
       </c>
       <c r="H8">
-        <v>0.1909090909090909</v>
+        <v>0.02895522388059701</v>
       </c>
       <c r="I8">
-        <v>0.1397727272727273</v>
+        <v>-0.0117910447761194</v>
       </c>
       <c r="J8">
-        <v>0.1357562695924765</v>
+        <v>-0.005895522388059702</v>
       </c>
       <c r="K8">
-        <v>0.339</v>
+        <v>-0.028</v>
       </c>
       <c r="L8">
-        <v>0.1284090909090909</v>
+        <v>-0.00417910447761194</v>
       </c>
       <c r="M8">
-        <v>0.348</v>
+        <v>0.118</v>
       </c>
       <c r="N8">
-        <v>0.02083832335329341</v>
+        <v>0.01072727272727273</v>
       </c>
       <c r="O8">
-        <v>1.026548672566372</v>
+        <v>-4.214285714285714</v>
       </c>
       <c r="P8">
-        <v>0.348</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.02083832335329341</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>1.026548672566372</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>0.74</v>
+        <v>0.781</v>
       </c>
       <c r="V8">
-        <v>0.04431137724550898</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="W8">
-        <v>0.02778688524590164</v>
+        <v>-0.001296296296296296</v>
       </c>
       <c r="X8">
-        <v>0.06338053564601141</v>
+        <v>0.1027143423033656</v>
       </c>
       <c r="Y8">
-        <v>-0.03559365040010977</v>
+        <v>-0.1040106385996619</v>
       </c>
       <c r="Z8">
-        <v>0.2205329546403809</v>
+        <v>0.3175054497204057</v>
       </c>
       <c r="AA8">
-        <v>0.02993873124418494</v>
+        <v>-0.001871860487157615</v>
       </c>
       <c r="AB8">
-        <v>0.06323373419439933</v>
+        <v>0.1025963797644202</v>
       </c>
       <c r="AC8">
-        <v>-0.03329500295021439</v>
+        <v>-0.1044682402515778</v>
       </c>
       <c r="AD8">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="AG8">
-        <v>-0.669</v>
+        <v>-0.745</v>
       </c>
       <c r="AH8">
-        <v>0.004233498300638005</v>
+        <v>0.00326205146792316</v>
       </c>
       <c r="AI8">
-        <v>0.00535001130284078</v>
+        <v>0.001796765821521261</v>
       </c>
       <c r="AJ8">
-        <v>-0.04173164493793276</v>
+        <v>-0.07264748902974158</v>
       </c>
       <c r="AK8">
-        <v>-0.05338759875508739</v>
+        <v>-0.03869124902622696</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="AN8">
-        <v>0.1666666666666667</v>
+        <v>-7.199999999999999</v>
+      </c>
+      <c r="AO8">
+        <v>-2.257142857142857</v>
       </c>
       <c r="AP8">
-        <v>-1.570422535211268</v>
+        <v>149</v>
+      </c>
+      <c r="AQ8">
+        <v>-2.257142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -1499,7 +1502,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Asuransi Jasa Tania Tbk (IDX:ASJT)</t>
+          <t>PT Asuransi Bintang Tbk (IDX:ASBI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1508,115 +1511,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.123</v>
+        <v>-0.00017</v>
+      </c>
+      <c r="E9">
+        <v>0.07389999999999999</v>
       </c>
       <c r="G9">
-        <v>-0.0300498753117207</v>
+        <v>-0.03909090909090909</v>
       </c>
       <c r="H9">
-        <v>-0.0300498753117207</v>
+        <v>-0.03909090909090909</v>
       </c>
       <c r="I9">
-        <v>-0.04638403990024938</v>
+        <v>-0.02928571428571429</v>
       </c>
       <c r="J9">
-        <v>-0.04638403990024938</v>
+        <v>-0.02928571428571429</v>
       </c>
       <c r="K9">
-        <v>-0.495</v>
+        <v>1.65</v>
       </c>
       <c r="L9">
-        <v>-0.06172069825436409</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.143</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.01191666666666667</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.08666666666666667</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.143</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.01191666666666667</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.08666666666666667</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.652</v>
+        <v>1.3</v>
       </c>
       <c r="V9">
-        <v>0.04794117647058824</v>
+        <v>0.1083333333333333</v>
       </c>
       <c r="W9">
-        <v>-0.03485915492957747</v>
+        <v>0.07674418604651162</v>
       </c>
       <c r="X9">
-        <v>0.06360186100257935</v>
+        <v>0.1025912139355573</v>
       </c>
       <c r="Y9">
-        <v>-0.09846101593215681</v>
+        <v>-0.02584702788904565</v>
       </c>
       <c r="Z9">
-        <v>0.6004791853848457</v>
+        <v>0.7544951251776003</v>
       </c>
       <c r="AA9">
-        <v>-0.02785265049415993</v>
+        <v>-0.02209592866591544</v>
       </c>
       <c r="AB9">
-        <v>0.06321112286977847</v>
+        <v>0.102558437768431</v>
       </c>
       <c r="AC9">
-        <v>-0.09106377336393839</v>
+        <v>-0.1246543664343465</v>
       </c>
       <c r="AD9">
-        <v>0.154</v>
+        <v>0.012</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.154</v>
+        <v>0.012</v>
       </c>
       <c r="AG9">
-        <v>-0.498</v>
+        <v>-1.288</v>
       </c>
       <c r="AH9">
-        <v>0.01119674276574088</v>
+        <v>0.000999000999000999</v>
       </c>
       <c r="AI9">
-        <v>0.007079157856026477</v>
+        <v>0.0005147563486616335</v>
       </c>
       <c r="AJ9">
-        <v>-0.03800946420393833</v>
+        <v>-0.1202389843166542</v>
       </c>
       <c r="AK9">
-        <v>-0.02359965880011373</v>
+        <v>-0.05851353807014356</v>
       </c>
       <c r="AL9">
-        <v>0.046</v>
+        <v>0.005</v>
       </c>
       <c r="AM9">
-        <v>0.046</v>
+        <v>0.005</v>
       </c>
       <c r="AN9">
-        <v>-0.8415300546448088</v>
+        <v>-0.05084745762711865</v>
       </c>
       <c r="AO9">
-        <v>-8.086956521739131</v>
+        <v>-90.2</v>
       </c>
       <c r="AP9">
-        <v>2.721311475409836</v>
+        <v>5.457627118644068</v>
       </c>
       <c r="AQ9">
-        <v>-8.086956521739131</v>
+        <v>-90.2</v>
       </c>
     </row>
     <row r="10">
@@ -1627,7 +1636,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Asuransi Bintang Tbk (IDX:ASBI)</t>
+          <t>PT Asuransi Harta Aman Pratama Tbk (IDX:AHAP)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1636,121 +1645,115 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0168</v>
-      </c>
-      <c r="E10">
-        <v>-0.0212</v>
+        <v>-0.00038</v>
       </c>
       <c r="G10">
-        <v>-0.0395364238410596</v>
+        <v>-0.07204968944099378</v>
       </c>
       <c r="H10">
-        <v>-0.0395364238410596</v>
+        <v>-0.07204968944099378</v>
       </c>
       <c r="I10">
-        <v>-0.1</v>
+        <v>-0.106832298136646</v>
       </c>
       <c r="J10">
-        <v>-0.1</v>
+        <v>-0.106832298136646</v>
       </c>
       <c r="K10">
-        <v>1.34</v>
+        <v>-1.73</v>
       </c>
       <c r="L10">
-        <v>0.08874172185430464</v>
+        <v>-0.1074534161490683</v>
       </c>
       <c r="M10">
-        <v>0.251</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.03500697350069735</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.1873134328358209</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.251</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.03500697350069735</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.1873134328358209</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>1.13</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="V10">
-        <v>0.1576011157601116</v>
+        <v>0.03879668049792531</v>
       </c>
       <c r="W10">
-        <v>0.06836734693877551</v>
+        <v>-0.1733466933867735</v>
       </c>
       <c r="X10">
-        <v>0.06342643959042754</v>
+        <v>0.1028180358034917</v>
       </c>
       <c r="Y10">
-        <v>0.00494090734834797</v>
+        <v>-0.2761647291902652</v>
       </c>
       <c r="Z10">
-        <v>0.8737414651082048</v>
+        <v>1.791675940351658</v>
       </c>
       <c r="AA10">
-        <v>-0.08737414651082048</v>
+        <v>-0.1914088582239038</v>
       </c>
       <c r="AB10">
-        <v>0.06324027826052427</v>
+        <v>0.1026475726189649</v>
       </c>
       <c r="AC10">
-        <v>-0.1506144247713447</v>
+        <v>-0.2940564308428687</v>
       </c>
       <c r="AD10">
-        <v>0.041</v>
+        <v>0.125</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.041</v>
+        <v>0.125</v>
       </c>
       <c r="AG10">
-        <v>-1.089</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.005685757869920954</v>
+        <v>0.005159958720330237</v>
       </c>
       <c r="AI10">
-        <v>0.001903347105519707</v>
+        <v>0.008787346221441126</v>
       </c>
       <c r="AJ10">
-        <v>-0.1790823877651702</v>
+        <v>-0.0347788750536711</v>
       </c>
       <c r="AK10">
-        <v>-0.05335358385184459</v>
+        <v>-0.06094808126410836</v>
       </c>
       <c r="AL10">
-        <v>0.008999999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="AM10">
-        <v>0.008999999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="AN10">
-        <v>-0.03445378151260504</v>
+        <v>-0.0791139240506329</v>
       </c>
       <c r="AO10">
-        <v>-167.7777777777778</v>
+        <v>-33.07692307692308</v>
       </c>
       <c r="AP10">
-        <v>0.915126050420168</v>
+        <v>0.5126582278481012</v>
       </c>
       <c r="AQ10">
-        <v>-167.7777777777778</v>
+        <v>-33.07692307692308</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00038</v>
+        <v>0.08074999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0233</v>
+        <v>0.008200000000000002</v>
       </c>
       <c r="G2">
-        <v>0.1015226792718495</v>
+        <v>0.08112938287174551</v>
       </c>
       <c r="H2">
-        <v>0.1015226792718495</v>
+        <v>0.08112938287174551</v>
       </c>
       <c r="I2">
-        <v>0.06275973046364276</v>
+        <v>0.1787348787813418</v>
       </c>
       <c r="J2">
-        <v>0.0543945960915324</v>
+        <v>0.1483860438188619</v>
       </c>
       <c r="K2">
-        <v>35.709</v>
+        <v>84.887</v>
       </c>
       <c r="L2">
-        <v>0.0718274162727547</v>
+        <v>0.1408608930853094</v>
       </c>
       <c r="M2">
-        <v>18.045</v>
+        <v>12.613</v>
       </c>
       <c r="N2">
-        <v>0.04335655934646805</v>
+        <v>0.02943523920653442</v>
       </c>
       <c r="O2">
-        <v>0.5053347895488534</v>
+        <v>0.1485857669607832</v>
       </c>
       <c r="P2">
-        <v>17.927</v>
+        <v>12.613</v>
       </c>
       <c r="Q2">
-        <v>0.04307304180682364</v>
+        <v>0.02943523920653442</v>
       </c>
       <c r="R2">
-        <v>0.5020303004844717</v>
+        <v>0.1485857669607832</v>
       </c>
       <c r="S2">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.00653920753671377</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>55.844</v>
+        <v>36.7</v>
       </c>
       <c r="V2">
-        <v>0.1341758769822201</v>
+        <v>0.08564760793465578</v>
       </c>
       <c r="W2">
-        <v>0.04617424242424242</v>
+        <v>0.0448673597750481</v>
       </c>
       <c r="X2">
-        <v>0.1027661890534286</v>
+        <v>0.08771733905392351</v>
       </c>
       <c r="Y2">
-        <v>-0.05659194662918621</v>
+        <v>-0.04284997927887541</v>
       </c>
       <c r="Z2">
-        <v>0.6772597917611751</v>
+        <v>0.8714633811269459</v>
       </c>
       <c r="AA2">
-        <v>0.03448599823649693</v>
+        <v>0.03228805377532364</v>
       </c>
       <c r="AB2">
-        <v>0.1026263935157848</v>
+        <v>0.08759711552102212</v>
       </c>
       <c r="AC2">
-        <v>-0.06862680572859045</v>
+        <v>-0.05532144093365145</v>
       </c>
       <c r="AD2">
-        <v>13.659</v>
+        <v>17.973</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.659</v>
+        <v>17.973</v>
       </c>
       <c r="AG2">
-        <v>-42.185</v>
+        <v>-18.727</v>
       </c>
       <c r="AH2">
-        <v>0.03177553569891523</v>
+        <v>0.04025551377126948</v>
       </c>
       <c r="AI2">
-        <v>0.01721016204692443</v>
+        <v>0.02082683931015223</v>
       </c>
       <c r="AJ2">
-        <v>-0.1127895940002406</v>
+        <v>-0.0457009124564088</v>
       </c>
       <c r="AK2">
-        <v>-0.05717557924411946</v>
+        <v>-0.02266442204937109</v>
       </c>
       <c r="AL2">
-        <v>1.199</v>
+        <v>0.391</v>
       </c>
       <c r="AM2">
-        <v>1.199</v>
+        <v>0.391</v>
       </c>
       <c r="AN2">
-        <v>0.3059263572836409</v>
+        <v>0.1530776503053377</v>
       </c>
       <c r="AO2">
-        <v>26.02251876563803</v>
+        <v>275.4757033248082</v>
       </c>
       <c r="AP2">
-        <v>-0.9448351549901451</v>
+        <v>-0.1594995358186201</v>
       </c>
       <c r="AQ2">
-        <v>26.02251876563803</v>
+        <v>275.4757033248082</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Lippo General Insurance Tbk (IDX:LPGI)</t>
+          <t>PT Asuransi Ramayana Tbk (IDX:ASRM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.132</v>
+        <v>0.155</v>
       </c>
       <c r="E3">
-        <v>-0.0107</v>
+        <v>0.0549</v>
       </c>
       <c r="G3">
-        <v>0.0781733746130031</v>
+        <v>0.0425233644859813</v>
       </c>
       <c r="H3">
-        <v>0.0781733746130031</v>
+        <v>0.0425233644859813</v>
       </c>
       <c r="I3">
-        <v>0.07082043343653252</v>
+        <v>0.04314641744548287</v>
       </c>
       <c r="J3">
-        <v>0.0548031017621018</v>
+        <v>0.04096396970780786</v>
       </c>
       <c r="K3">
-        <v>8.27</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
-        <v>0.0640092879256966</v>
+        <v>0.04439252336448598</v>
       </c>
       <c r="M3">
-        <v>6.56</v>
+        <v>1.26</v>
       </c>
       <c r="N3">
-        <v>0.05841495992876224</v>
+        <v>0.04064516129032258</v>
       </c>
       <c r="O3">
-        <v>0.7932285368802902</v>
+        <v>0.2210526315789474</v>
       </c>
       <c r="P3">
-        <v>6.56</v>
+        <v>1.26</v>
       </c>
       <c r="Q3">
-        <v>0.05841495992876224</v>
+        <v>0.04064516129032258</v>
       </c>
       <c r="R3">
-        <v>0.7932285368802902</v>
+        <v>0.2210526315789474</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>5.71</v>
       </c>
       <c r="V3">
-        <v>0.0201246660730187</v>
+        <v>0.1841935483870968</v>
       </c>
       <c r="W3">
-        <v>0.1174715909090909</v>
+        <v>0.1488250652741515</v>
       </c>
       <c r="X3">
-        <v>0.1025577817878172</v>
+        <v>0.08829940120447577</v>
       </c>
       <c r="Y3">
-        <v>0.01491380912127371</v>
+        <v>0.06052566406967569</v>
       </c>
       <c r="Z3">
-        <v>1.874528466136614</v>
+        <v>3.947732513451192</v>
       </c>
       <c r="AA3">
-        <v>0.1027299742856414</v>
+        <v>0.1617147950955428</v>
       </c>
       <c r="AB3">
-        <v>0.102545236751818</v>
+        <v>0.08772273747707343</v>
       </c>
       <c r="AC3">
-        <v>0.0001847375338234758</v>
+        <v>0.07399205761846936</v>
       </c>
       <c r="AD3">
-        <v>0.043</v>
+        <v>0.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.043</v>
+        <v>0.6</v>
       </c>
       <c r="AG3">
-        <v>-2.217</v>
+        <v>-5.11</v>
       </c>
       <c r="AH3">
-        <v>0.0003827563800147761</v>
+        <v>0.0189873417721519</v>
       </c>
       <c r="AI3">
-        <v>0.0007854885556144163</v>
+        <v>0.01415094339622642</v>
       </c>
       <c r="AJ3">
-        <v>-0.02013934939999818</v>
+        <v>-0.1973735032831209</v>
       </c>
       <c r="AK3">
-        <v>-0.04224224987138692</v>
+        <v>-0.1392750068138457</v>
       </c>
       <c r="AL3">
-        <v>0.018</v>
+        <v>0.121</v>
       </c>
       <c r="AM3">
-        <v>0.018</v>
+        <v>0.121</v>
       </c>
       <c r="AN3">
-        <v>0.004401228249744114</v>
+        <v>0.1125703564727955</v>
       </c>
       <c r="AO3">
-        <v>508.3333333333334</v>
+        <v>45.78512396694215</v>
       </c>
       <c r="AP3">
-        <v>-0.2269191402251791</v>
+        <v>-0.9587242026266417</v>
       </c>
       <c r="AQ3">
-        <v>508.3333333333334</v>
+        <v>45.78512396694215</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Asuransi Ramayana Tbk (IDX:ASRM)</t>
+          <t>PT Asuransi Tugu Pratama Indonesia Tbk (IDX:TUGU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.197</v>
+        <v>0.0722</v>
       </c>
       <c r="E4">
-        <v>0.0233</v>
+        <v>0.322</v>
       </c>
       <c r="G4">
-        <v>0.03684633950120676</v>
+        <v>0.1547826086956522</v>
       </c>
       <c r="H4">
-        <v>0.03684633950120676</v>
+        <v>0.1547826086956522</v>
       </c>
       <c r="I4">
-        <v>0.02727272727272727</v>
+        <v>0.4447826086956522</v>
       </c>
       <c r="J4">
-        <v>0.02295078888054095</v>
+        <v>0.3504477175999333</v>
       </c>
       <c r="K4">
-        <v>4.07</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L4">
-        <v>0.03274336283185841</v>
+        <v>0.3473913043478261</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>8.92</v>
       </c>
       <c r="N4">
-        <v>0.03249211356466877</v>
+        <v>0.03784471786168859</v>
       </c>
       <c r="O4">
-        <v>0.2530712530712531</v>
+        <v>0.111639549436796</v>
       </c>
       <c r="P4">
-        <v>1.03</v>
+        <v>8.92</v>
       </c>
       <c r="Q4">
-        <v>0.03249211356466877</v>
+        <v>0.03784471786168859</v>
       </c>
       <c r="R4">
-        <v>0.2530712530712531</v>
+        <v>0.111639549436796</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.55</v>
+        <v>25.2</v>
       </c>
       <c r="V4">
-        <v>0.2066246056782334</v>
+        <v>0.1069155706406449</v>
       </c>
       <c r="W4">
-        <v>0.1068241469816273</v>
+        <v>0.1456700091157703</v>
       </c>
       <c r="X4">
-        <v>0.1038615413471803</v>
+        <v>0.09025814195788578</v>
       </c>
       <c r="Y4">
-        <v>0.002962605634447044</v>
+        <v>0.05541186715788451</v>
       </c>
       <c r="Z4">
-        <v>3.623906705539359</v>
+        <v>0.4437584410573028</v>
       </c>
       <c r="AA4">
-        <v>0.08317151772161049</v>
+        <v>0.1555141328342363</v>
       </c>
       <c r="AB4">
-        <v>0.102814980614421</v>
+        <v>0.08811905344379486</v>
       </c>
       <c r="AC4">
-        <v>-0.01964346289281046</v>
+        <v>0.0673950793904414</v>
       </c>
       <c r="AD4">
-        <v>0.775</v>
+        <v>16.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.775</v>
+        <v>16.7</v>
       </c>
       <c r="AG4">
-        <v>-5.774999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="AH4">
-        <v>0.02386451116243264</v>
+        <v>0.06616481774960381</v>
       </c>
       <c r="AI4">
-        <v>0.01983365323096609</v>
+        <v>0.0248032080796079</v>
       </c>
       <c r="AJ4">
-        <v>-0.2227579556412729</v>
+        <v>-0.03741197183098591</v>
       </c>
       <c r="AK4">
-        <v>-0.1775557263643351</v>
+        <v>-0.01311525999074217</v>
       </c>
       <c r="AL4">
-        <v>0.139</v>
+        <v>0.241</v>
       </c>
       <c r="AM4">
-        <v>0.139</v>
+        <v>0.241</v>
       </c>
       <c r="AN4">
-        <v>0.1942355889724311</v>
+        <v>0.1504504504504504</v>
       </c>
       <c r="AO4">
-        <v>24.38848920863309</v>
+        <v>424.4813278008299</v>
       </c>
       <c r="AP4">
-        <v>-1.447368421052631</v>
+        <v>-0.07657657657657657</v>
       </c>
       <c r="AQ4">
-        <v>24.38848920863309</v>
+        <v>424.4813278008299</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Asuransi Dayin Mitra Tbk (IDX:ASDM)</t>
+          <t>PT Victoria Insurance Tbk (IDX:VINS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0162</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.156</v>
+        <v>-0.0305</v>
       </c>
       <c r="G5">
-        <v>0.1745614035087719</v>
+        <v>0.1544080604534005</v>
       </c>
       <c r="H5">
-        <v>0.1745614035087719</v>
+        <v>0.1544080604534005</v>
       </c>
       <c r="I5">
-        <v>0.09035087719298246</v>
+        <v>0.2277078085642317</v>
       </c>
       <c r="J5">
-        <v>0.08673684210526315</v>
+        <v>0.222538225883314</v>
       </c>
       <c r="K5">
-        <v>1.24</v>
+        <v>0.904</v>
       </c>
       <c r="L5">
-        <v>0.1087719298245614</v>
+        <v>0.2277078085642317</v>
       </c>
       <c r="M5">
-        <v>0.908</v>
+        <v>0.444</v>
       </c>
       <c r="N5">
-        <v>0.08180180180180181</v>
+        <v>0.03126760563380282</v>
       </c>
       <c r="O5">
-        <v>0.7322580645161291</v>
+        <v>0.4911504424778761</v>
       </c>
       <c r="P5">
-        <v>0.908</v>
+        <v>0.444</v>
       </c>
       <c r="Q5">
-        <v>0.08180180180180181</v>
+        <v>0.03126760563380282</v>
       </c>
       <c r="R5">
-        <v>0.7322580645161291</v>
+        <v>0.4911504424778761</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1038,73 +1038,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.889</v>
+        <v>0.327</v>
       </c>
       <c r="V5">
-        <v>0.08009009009009009</v>
+        <v>0.02302816901408451</v>
       </c>
       <c r="W5">
-        <v>0.05166666666666667</v>
+        <v>0.07793103448275862</v>
       </c>
       <c r="X5">
-        <v>0.1030983253285956</v>
+        <v>0.08760876892167976</v>
       </c>
       <c r="Y5">
-        <v>-0.05143165866192893</v>
+        <v>-0.009677734438921143</v>
       </c>
       <c r="Z5">
-        <v>0.4870337933096937</v>
+        <v>0.3537063435495367</v>
       </c>
       <c r="AA5">
-        <v>0.04224377323023027</v>
+        <v>0.07871318217718788</v>
       </c>
       <c r="AB5">
-        <v>0.1027566983746112</v>
+        <v>0.08757078928825077</v>
       </c>
       <c r="AC5">
-        <v>-0.06051292514438091</v>
+        <v>-0.008857607111062885</v>
       </c>
       <c r="AD5">
-        <v>0.115</v>
+        <v>0.017</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.115</v>
+        <v>0.017</v>
       </c>
       <c r="AG5">
-        <v>-0.774</v>
+        <v>-0.31</v>
       </c>
       <c r="AH5">
-        <v>0.01025412394115024</v>
+        <v>0.001195751565027784</v>
       </c>
       <c r="AI5">
-        <v>0.004932446922582029</v>
+        <v>0.001647765823398275</v>
       </c>
       <c r="AJ5">
-        <v>-0.07495642068564788</v>
+        <v>-0.02231821454283657</v>
       </c>
       <c r="AK5">
-        <v>-0.03451351110318381</v>
+        <v>-0.03103103103103103</v>
       </c>
       <c r="AL5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.09583333333333334</v>
-      </c>
-      <c r="AO5">
-        <v>41.2</v>
+        <v>0.01756198347107438</v>
       </c>
       <c r="AP5">
-        <v>-0.645</v>
-      </c>
-      <c r="AQ5">
-        <v>41.2</v>
+        <v>-0.3202479338842975</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Victoria Insurance Tbk (IDX:VINS)</t>
+          <t>PT Asuransi Dayin Mitra Tbk (IDX:ASDM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1124,46 +1118,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0153</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="E6">
-        <v>0.158</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G6">
-        <v>0.3163636363636363</v>
+        <v>0.1291338582677165</v>
       </c>
       <c r="H6">
-        <v>0.3163636363636363</v>
+        <v>0.1291338582677165</v>
       </c>
       <c r="I6">
-        <v>0.1749090909090909</v>
+        <v>0.1377952755905512</v>
       </c>
       <c r="J6">
-        <v>0.1749090909090909</v>
+        <v>0.1016050878255603</v>
       </c>
       <c r="K6">
-        <v>0.537</v>
+        <v>1.35</v>
       </c>
       <c r="L6">
-        <v>0.1952727272727273</v>
+        <v>0.1062992125984252</v>
       </c>
       <c r="M6">
-        <v>0.326</v>
+        <v>0.819</v>
       </c>
       <c r="N6">
-        <v>0.01963855421686747</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O6">
-        <v>0.6070763500931099</v>
+        <v>0.6066666666666666</v>
       </c>
       <c r="P6">
-        <v>0.326</v>
+        <v>0.819</v>
       </c>
       <c r="Q6">
-        <v>0.01963855421686747</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R6">
-        <v>0.6070763500931099</v>
+        <v>0.6066666666666666</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1172,67 +1166,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.429</v>
+        <v>1.26</v>
       </c>
       <c r="V6">
-        <v>0.0258433734939759</v>
+        <v>0.1076923076923077</v>
       </c>
       <c r="W6">
-        <v>0.04068181818181819</v>
+        <v>0.0581896551724138</v>
       </c>
       <c r="X6">
-        <v>0.1027100105583776</v>
+        <v>0.08858726158392216</v>
       </c>
       <c r="Y6">
-        <v>-0.06202819237655945</v>
+        <v>-0.03039760641150836</v>
       </c>
       <c r="Z6">
-        <v>0.2194557497406432</v>
+        <v>0.5663069651297601</v>
       </c>
       <c r="AA6">
-        <v>0.03838480568190887</v>
+        <v>0.05753966892823578</v>
       </c>
       <c r="AB6">
-        <v>0.1026052144126047</v>
+        <v>0.0876100406969367</v>
       </c>
       <c r="AC6">
-        <v>-0.0642204087306958</v>
+        <v>-0.03007037176870093</v>
       </c>
       <c r="AD6">
-        <v>0.053</v>
+        <v>0.315</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.053</v>
+        <v>0.315</v>
       </c>
       <c r="AG6">
-        <v>-0.376</v>
+        <v>-0.9450000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.003182609739986789</v>
+        <v>0.02621722846441948</v>
       </c>
       <c r="AI6">
-        <v>0.004548185016733888</v>
+        <v>0.01328273244781784</v>
       </c>
       <c r="AJ6">
-        <v>-0.02317554240631164</v>
+        <v>-0.08786610878661089</v>
       </c>
       <c r="AK6">
-        <v>-0.03349964362081254</v>
+        <v>-0.04208416833667335</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AN6">
-        <v>0.1041257367387033</v>
+        <v>0.1702702702702703</v>
+      </c>
+      <c r="AO6">
+        <v>175</v>
       </c>
       <c r="AP6">
-        <v>-0.7387033398821218</v>
+        <v>-0.5108108108108108</v>
+      </c>
+      <c r="AQ6">
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Asuransi Tugu Pratama Indonesia Tbk (IDX:TUGU)</t>
+          <t>PT Asuransi Bintang Tbk (IDX:ASBI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1251,41 +1251,47 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.0307</v>
+      </c>
+      <c r="E7">
+        <v>0.0469</v>
+      </c>
       <c r="G7">
-        <v>0.1803450078410873</v>
+        <v>-0.01013793103448276</v>
       </c>
       <c r="H7">
-        <v>0.1803450078410873</v>
+        <v>-0.01013793103448276</v>
       </c>
       <c r="I7">
-        <v>0.1014113957135389</v>
+        <v>0.01675862068965517</v>
       </c>
       <c r="J7">
-        <v>0.08704478132078758</v>
+        <v>0.01068179910044977</v>
       </c>
       <c r="K7">
-        <v>21.7</v>
+        <v>0.735</v>
       </c>
       <c r="L7">
-        <v>0.1134343962362781</v>
+        <v>0.05068965517241379</v>
       </c>
       <c r="M7">
-        <v>8.960000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N7">
-        <v>0.04539007092198582</v>
+        <v>0.007547169811320754</v>
       </c>
       <c r="O7">
-        <v>0.4129032258064517</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="P7">
-        <v>8.960000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="Q7">
-        <v>0.04539007092198582</v>
+        <v>0.007547169811320754</v>
       </c>
       <c r="R7">
-        <v>0.4129032258064517</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1294,73 +1300,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>42.7</v>
+        <v>0.986</v>
       </c>
       <c r="V7">
-        <v>0.2163120567375887</v>
+        <v>0.0620125786163522</v>
       </c>
       <c r="W7">
-        <v>0.03885407341092211</v>
+        <v>0.0315450643776824</v>
       </c>
       <c r="X7">
-        <v>0.1059676657361218</v>
+        <v>0.08777135147779938</v>
       </c>
       <c r="Y7">
-        <v>-0.06711359232519964</v>
+        <v>-0.05622628710011698</v>
       </c>
       <c r="Z7">
-        <v>0.3513960323291698</v>
+        <v>0.6587316009449391</v>
       </c>
       <c r="AA7">
-        <v>0.03058719079108499</v>
+        <v>0.00703643862241149</v>
       </c>
       <c r="AB7">
-        <v>0.1036203935175701</v>
+        <v>0.08760894872101345</v>
       </c>
       <c r="AC7">
-        <v>-0.07303320272648509</v>
+        <v>-0.08057251009860196</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AG7">
-        <v>-30.2</v>
+        <v>-0.899</v>
       </c>
       <c r="AH7">
-        <v>0.05955216769890424</v>
+        <v>0.005441921561268531</v>
       </c>
       <c r="AI7">
-        <v>0.02058290795323563</v>
+        <v>0.003440503025269901</v>
       </c>
       <c r="AJ7">
-        <v>-0.180622009569378</v>
+        <v>-0.05992933804413039</v>
       </c>
       <c r="AK7">
-        <v>-0.05348919589089622</v>
+        <v>-0.03699436237191885</v>
       </c>
       <c r="AL7">
-        <v>0.925</v>
+        <v>0.002</v>
       </c>
       <c r="AM7">
-        <v>0.925</v>
+        <v>0.002</v>
       </c>
       <c r="AN7">
-        <v>0.4032258064516129</v>
+        <v>0.1663479923518164</v>
       </c>
       <c r="AO7">
-        <v>20.97297297297297</v>
+        <v>121.5</v>
       </c>
       <c r="AP7">
-        <v>-0.9741935483870968</v>
+        <v>-1.718929254302103</v>
       </c>
       <c r="AQ7">
-        <v>20.97297297297297</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="8">
@@ -1380,34 +1386,37 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.108</v>
+        <v>-0.09849999999999999</v>
+      </c>
+      <c r="E8">
+        <v>-0.53</v>
       </c>
       <c r="G8">
-        <v>0.02895522388059701</v>
+        <v>0.01148825065274151</v>
       </c>
       <c r="H8">
-        <v>0.02895522388059701</v>
+        <v>0.01148825065274151</v>
       </c>
       <c r="I8">
-        <v>-0.0117910447761194</v>
+        <v>-0.000783289817232376</v>
       </c>
       <c r="J8">
-        <v>-0.005895522388059702</v>
+        <v>-0.0004325630333969838</v>
       </c>
       <c r="K8">
-        <v>-0.028</v>
+        <v>0.038</v>
       </c>
       <c r="L8">
-        <v>-0.00417910447761194</v>
+        <v>0.004960835509138381</v>
       </c>
       <c r="M8">
-        <v>0.118</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01072727272727273</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-4.214285714285714</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1416,82 +1425,79 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>0.118</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0.781</v>
+        <v>0.667</v>
       </c>
       <c r="V8">
-        <v>0.07100000000000001</v>
+        <v>0.05850877192982457</v>
       </c>
       <c r="W8">
-        <v>-0.001296296296296296</v>
+        <v>0.0019</v>
       </c>
       <c r="X8">
-        <v>0.1027143423033656</v>
+        <v>0.08766332663004764</v>
       </c>
       <c r="Y8">
-        <v>-0.1040106385996619</v>
+        <v>-0.08576332663004764</v>
       </c>
       <c r="Z8">
-        <v>0.3175054497204057</v>
+        <v>0.3978187483770449</v>
       </c>
       <c r="AA8">
-        <v>-0.001871860487157615</v>
+        <v>-0.000172081684540166</v>
       </c>
       <c r="AB8">
-        <v>0.1025963797644202</v>
+        <v>0.08758528232103077</v>
       </c>
       <c r="AC8">
-        <v>-0.1044682402515778</v>
+        <v>-0.08775736400557094</v>
       </c>
       <c r="AD8">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="AG8">
-        <v>-0.745</v>
+        <v>-0.637</v>
       </c>
       <c r="AH8">
-        <v>0.00326205146792316</v>
+        <v>0.002624671916010499</v>
       </c>
       <c r="AI8">
-        <v>0.001796765821521261</v>
+        <v>0.001447178002894356</v>
       </c>
       <c r="AJ8">
-        <v>-0.07264748902974158</v>
+        <v>-0.05918424231162316</v>
       </c>
       <c r="AK8">
-        <v>-0.03869124902622696</v>
+        <v>-0.03174998753925136</v>
       </c>
       <c r="AL8">
-        <v>0.035</v>
+        <v>0.005</v>
       </c>
       <c r="AM8">
-        <v>0.035</v>
+        <v>0.005</v>
       </c>
       <c r="AN8">
-        <v>-7.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-2.257142857142857</v>
+        <v>-1.2</v>
       </c>
       <c r="AP8">
-        <v>149</v>
+        <v>-63.7</v>
       </c>
       <c r="AQ8">
-        <v>-2.257142857142857</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Asuransi Bintang Tbk (IDX:ASBI)</t>
+          <t>PT Lippo General Insurance Tbk (IDX:LPGI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,46 +1517,43 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.00017</v>
-      </c>
-      <c r="E9">
-        <v>0.07389999999999999</v>
+        <v>0.199</v>
       </c>
       <c r="G9">
-        <v>-0.03909090909090909</v>
+        <v>0.03342203299627462</v>
       </c>
       <c r="H9">
-        <v>-0.03909090909090909</v>
+        <v>0.03342203299627462</v>
       </c>
       <c r="I9">
-        <v>-0.02928571428571429</v>
+        <v>-0.009952102182011709</v>
       </c>
       <c r="J9">
-        <v>-0.02928571428571429</v>
+        <v>-0.009952102182011709</v>
       </c>
       <c r="K9">
-        <v>1.65</v>
+        <v>-2.64</v>
       </c>
       <c r="L9">
-        <v>0.1071428571428571</v>
+        <v>-0.01405002660989888</v>
       </c>
       <c r="M9">
-        <v>0.143</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>0.01191666666666667</v>
+        <v>0.01329113924050633</v>
       </c>
       <c r="O9">
-        <v>0.08666666666666667</v>
+        <v>-0.3977272727272727</v>
       </c>
       <c r="P9">
-        <v>0.143</v>
+        <v>1.05</v>
       </c>
       <c r="Q9">
-        <v>0.01191666666666667</v>
+        <v>0.01329113924050633</v>
       </c>
       <c r="R9">
-        <v>0.08666666666666667</v>
+        <v>-0.3977272727272727</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1559,73 +1562,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="V9">
-        <v>0.1083333333333333</v>
+        <v>0.01924050632911392</v>
       </c>
       <c r="W9">
-        <v>0.07674418604651162</v>
+        <v>-0.04826325411334552</v>
       </c>
       <c r="X9">
-        <v>0.1025912139355573</v>
+        <v>0.08763737848214473</v>
       </c>
       <c r="Y9">
-        <v>-0.02584702788904565</v>
+        <v>-0.1359006325954902</v>
       </c>
       <c r="Z9">
-        <v>0.7544951251776003</v>
+        <v>3.580206924146867</v>
       </c>
       <c r="AA9">
-        <v>-0.02209592866591544</v>
+        <v>-0.03563058514185546</v>
       </c>
       <c r="AB9">
-        <v>0.102558437768431</v>
+        <v>0.08757957754002584</v>
       </c>
       <c r="AC9">
-        <v>-0.1246543664343465</v>
+        <v>-0.1232101626818813</v>
       </c>
       <c r="AD9">
-        <v>0.012</v>
+        <v>0.154</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.012</v>
+        <v>0.154</v>
       </c>
       <c r="AG9">
-        <v>-1.288</v>
+        <v>-1.366</v>
       </c>
       <c r="AH9">
-        <v>0.000999000999000999</v>
+        <v>0.001945574449806706</v>
       </c>
       <c r="AI9">
-        <v>0.0005147563486616335</v>
+        <v>0.002828075072538289</v>
       </c>
       <c r="AJ9">
-        <v>-0.1202389843166542</v>
+        <v>-0.01759538346600716</v>
       </c>
       <c r="AK9">
-        <v>-0.05851353807014356</v>
+        <v>-0.0258057203309782</v>
       </c>
       <c r="AL9">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AM9">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AN9">
-        <v>-0.05084745762711865</v>
+        <v>-0.1232</v>
       </c>
       <c r="AO9">
-        <v>-90.2</v>
+        <v>-935</v>
       </c>
       <c r="AP9">
-        <v>5.457627118644068</v>
+        <v>1.0928</v>
       </c>
       <c r="AQ9">
-        <v>-90.2</v>
+        <v>-935</v>
       </c>
     </row>
     <row r="10">
@@ -1645,25 +1648,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00038</v>
+        <v>0.229</v>
       </c>
       <c r="G10">
-        <v>-0.07204968944099378</v>
+        <v>-0.03674285714285715</v>
       </c>
       <c r="H10">
-        <v>-0.07204968944099378</v>
+        <v>-0.03674285714285715</v>
       </c>
       <c r="I10">
-        <v>-0.106832298136646</v>
+        <v>-0.06571428571428571</v>
       </c>
       <c r="J10">
-        <v>-0.106832298136646</v>
+        <v>-0.06571428571428571</v>
       </c>
       <c r="K10">
-        <v>-1.73</v>
+        <v>-1.1</v>
       </c>
       <c r="L10">
-        <v>-0.1074534161490683</v>
+        <v>-0.06285714285714286</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1687,73 +1690,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.9350000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="V10">
-        <v>0.03879668049792531</v>
+        <v>0.0347972972972973</v>
       </c>
       <c r="W10">
-        <v>-0.1733466933867735</v>
+        <v>-0.07801418439716312</v>
       </c>
       <c r="X10">
-        <v>0.1028180358034917</v>
+        <v>0.08765318207396625</v>
       </c>
       <c r="Y10">
-        <v>-0.2761647291902652</v>
+        <v>-0.1656673664711294</v>
       </c>
       <c r="Z10">
-        <v>1.791675940351658</v>
+        <v>1.316779533483823</v>
       </c>
       <c r="AA10">
-        <v>-0.1914088582239038</v>
+        <v>-0.08653122648607976</v>
       </c>
       <c r="AB10">
-        <v>0.1026475726189649</v>
+        <v>0.08758305293333415</v>
       </c>
       <c r="AC10">
-        <v>-0.2940564308428687</v>
+        <v>-0.1741142794194139</v>
       </c>
       <c r="AD10">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10">
-        <v>-0.8100000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="AH10">
-        <v>0.005159958720330237</v>
+        <v>0.002359285473542299</v>
       </c>
       <c r="AI10">
-        <v>0.008787346221441126</v>
+        <v>0.00548159749412686</v>
       </c>
       <c r="AJ10">
-        <v>-0.0347788750536711</v>
+        <v>-0.0335195530726257</v>
       </c>
       <c r="AK10">
-        <v>-0.06094808126410836</v>
+        <v>-0.08177172061328791</v>
       </c>
       <c r="AL10">
-        <v>0.052</v>
+        <v>0.01</v>
       </c>
       <c r="AM10">
-        <v>0.052</v>
+        <v>0.01</v>
       </c>
       <c r="AN10">
-        <v>-0.0791139240506329</v>
+        <v>-0.06862745098039216</v>
       </c>
       <c r="AO10">
-        <v>-33.07692307692308</v>
+        <v>-115</v>
       </c>
       <c r="AP10">
-        <v>0.5126582278481012</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="AQ10">
-        <v>-33.07692307692308</v>
+        <v>-115</v>
       </c>
     </row>
   </sheetData>
